--- a/Orders for Upload.xlsx
+++ b/Orders for Upload.xlsx
@@ -8,23 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myoffice.accenture.com/personal/annalyn_d_manalili_accenture_com/Documents/Desktop/Amazon Q/Pricing Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{82B005B2-AADB-4DE2-A374-3CFB8FCE4DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_5D4F677527E92212F1D4E7248E6A1E2DD8F98358" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F205B08-2F94-4006-9340-D23223AAA54A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{101477DB-C899-4B23-8992-0454AEAE480A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Equipment" sheetId="2" r:id="rId1"/>
-    <sheet name="Material" sheetId="1" r:id="rId2"/>
+    <sheet name="Equipment" sheetId="1" r:id="rId1"/>
+    <sheet name="Material" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Equipment!$B$1:$G$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Material!$A$1:$H$149</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -41,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="406">
   <si>
     <t>Type</t>
   </si>
@@ -64,441 +57,423 @@
     <t>Total Price</t>
   </si>
   <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>2026-01-06</t>
+  </si>
+  <si>
+    <t>Printixer.ph</t>
+  </si>
+  <si>
+    <t>12-in-1 Multifunctional Paper Cutter</t>
+  </si>
+  <si>
+    <t>Pink</t>
+  </si>
+  <si>
+    <t>2025-10-10</t>
+  </si>
+  <si>
+    <t>notebook for school</t>
+  </si>
+  <si>
+    <t>13pcs set NFS Metal Handle With Blades Knife Carving Tools</t>
+  </si>
+  <si>
+    <t>Tool</t>
+  </si>
+  <si>
+    <t>Digiprint Connection</t>
+  </si>
+  <si>
+    <t>2-in-1 Multi-Function Paper Cutter with scoring board</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>LumenLines</t>
+  </si>
+  <si>
+    <t>360 Rotation Heavy Duty Stapler</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPAL </t>
+  </si>
+  <si>
+    <t>3-Layer 18/30 Slots Storage Box</t>
+  </si>
+  <si>
+    <t>18-Grid</t>
+  </si>
+  <si>
+    <t>Deli Tools Official Store</t>
+  </si>
+  <si>
+    <t>5'' Sharp Mini Diagonal Side Cutting Pliers</t>
+  </si>
+  <si>
+    <t>6 Hole Puncher</t>
+  </si>
+  <si>
+    <t>6 mm</t>
+  </si>
+  <si>
+    <t>2025-11-11</t>
+  </si>
+  <si>
+    <t>Lalaka</t>
+  </si>
+  <si>
+    <t>6 Layer Metal Rack Steel Rack Shelf</t>
+  </si>
+  <si>
+    <t>100×40×120</t>
+  </si>
+  <si>
+    <t>2025-12-11</t>
+  </si>
+  <si>
+    <t>Creative Express</t>
+  </si>
+  <si>
+    <t>Automatic Mug Heat Press Machine</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>GadgetGo</t>
+  </si>
+  <si>
+    <t>Automatic Paper Shredder 8 Sheets Electric Cutter</t>
+  </si>
+  <si>
+    <t>7L</t>
+  </si>
+  <si>
+    <t>Shyvana.ph</t>
+  </si>
+  <si>
+    <t>Bone Folder Craft Tools</t>
+  </si>
+  <si>
+    <t>ADJ Digiprintz Custom</t>
+  </si>
+  <si>
+    <t>Book Binding Tool Starter Kit</t>
+  </si>
+  <si>
+    <t>2025-11-12</t>
+  </si>
+  <si>
+    <t>wclgdku74i</t>
+  </si>
+  <si>
+    <t>Book Press</t>
+  </si>
+  <si>
+    <t>20*30</t>
+  </si>
+  <si>
+    <t>gardendirect</t>
+  </si>
+  <si>
+    <t>Bookbinding Cover Tool 5 in 1 Book Cover Guide</t>
+  </si>
+  <si>
+    <t>Crystal Image</t>
+  </si>
+  <si>
+    <t>Brayer Roller</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>2025-10-24</t>
+  </si>
+  <si>
+    <t>GRD UNDERGROUND</t>
+  </si>
+  <si>
+    <t>Calendar Clipping Machine</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>2026-01-24</t>
+  </si>
+  <si>
+    <t>Bee Happy Crafts</t>
+  </si>
+  <si>
+    <t>Cinch V2</t>
+  </si>
+  <si>
+    <t>White Pink</t>
+  </si>
+  <si>
+    <t>Dragons Hardware</t>
+  </si>
+  <si>
+    <t>Clamp Clip</t>
+  </si>
+  <si>
+    <t>2025-10-18</t>
+  </si>
+  <si>
+    <t>dbcraftystation</t>
+  </si>
+  <si>
+    <t>Teal Blue</t>
+  </si>
+  <si>
+    <t>Yasen</t>
+  </si>
+  <si>
+    <t>Corner Rounder R4/R7/R10 3in1 Corner Puncher</t>
+  </si>
+  <si>
+    <t>Craft Weeding Tool Kit</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>cricut</t>
+  </si>
+  <si>
+    <t>Cricut Explore 4</t>
+  </si>
+  <si>
+    <t>2026-01-17</t>
+  </si>
+  <si>
+    <t>Cricut Explore Deep Point Blade/Deep Cut Blade</t>
+  </si>
+  <si>
+    <t>Thick Materials</t>
+  </si>
+  <si>
+    <t>daphne.home.ph</t>
+  </si>
+  <si>
+    <t>Cricut Explore Padded Dust Cover</t>
+  </si>
+  <si>
+    <t>Googlygooeys 3D Cricut Crafts</t>
+  </si>
+  <si>
+    <t>Cutting Mat for Cricut</t>
+  </si>
+  <si>
+    <t>Lilac Strong 12x12</t>
+  </si>
+  <si>
+    <t>ANT HOME</t>
+  </si>
+  <si>
+    <t>Detachable Tool Kit DIY Leather Sewing</t>
+  </si>
+  <si>
+    <t>2025-12-23</t>
+  </si>
+  <si>
+    <t>Concon.InkShop</t>
+  </si>
+  <si>
+    <t>Epson Printer L121</t>
+  </si>
+  <si>
+    <t>Sublimation</t>
+  </si>
+  <si>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>arlenemamadel online shop</t>
+  </si>
+  <si>
+    <t>Epson Printer L121 Dust Cover</t>
+  </si>
+  <si>
+    <t>EasyBuy Mall</t>
+  </si>
+  <si>
+    <t>Eyelet Plier Set Hole Punch</t>
+  </si>
+  <si>
+    <t>Hole Puncher Circle</t>
+  </si>
+  <si>
+    <t>Far Eastern Hardware</t>
+  </si>
+  <si>
+    <t>INGCO Scissors Stainless Steel</t>
+  </si>
+  <si>
+    <t>11"</t>
+  </si>
+  <si>
+    <t>cafe.ph ( photolock.inc)</t>
+  </si>
+  <si>
+    <t>Laminator Machine</t>
+  </si>
+  <si>
+    <t>A3/A4</t>
+  </si>
+  <si>
+    <t>Min Shop</t>
+  </si>
+  <si>
+    <t>Long arm heavy duty Stapler</t>
+  </si>
+  <si>
+    <t>Vientiane</t>
+  </si>
+  <si>
+    <t>Mini Heat Press Machine for T Shirts Portable</t>
+  </si>
+  <si>
+    <t>2025-12-27</t>
+  </si>
+  <si>
+    <t>rules.ph</t>
+  </si>
+  <si>
+    <t>Multiple Layers Desktop Printer Stand</t>
+  </si>
+  <si>
+    <t>2 Tier White</t>
+  </si>
+  <si>
+    <t>YAMIGO Philippines</t>
+  </si>
+  <si>
+    <t>Multi-Purpose Envelope Punch Board</t>
+  </si>
+  <si>
+    <t>Officom Hot Melt Binding Machine</t>
+  </si>
+  <si>
+    <t>50 mm</t>
+  </si>
+  <si>
+    <t>Officom Paper Cutter Metal</t>
+  </si>
+  <si>
+    <t>B3: 35.3cm x 50cm</t>
+  </si>
+  <si>
+    <t>Officom Ream Cutter</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>Douwells Arts and Crafts</t>
+  </si>
+  <si>
+    <t>Paper Punch Loose Leaf Hole Puncher</t>
+  </si>
+  <si>
+    <t>30 Holes</t>
+  </si>
+  <si>
+    <t>Louisfashion</t>
+  </si>
+  <si>
+    <t>Patchwork Ruler Quilting Acrylic</t>
+  </si>
+  <si>
+    <t>30*15</t>
+  </si>
+  <si>
+    <t>PVC Cutting Mat A3 A4 A5 elf-Healing Pad Cutting Board</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>2025-10-31</t>
+  </si>
+  <si>
+    <t>creativenest</t>
+  </si>
+  <si>
+    <t>Ream Cutter Cutting Guide</t>
+  </si>
+  <si>
+    <t>A5 &amp; A6</t>
+  </si>
+  <si>
+    <t>Knotjustcraft Online Shop</t>
+  </si>
+  <si>
+    <t>Squeegee Promax for Decal, Stickers, Phototop Application</t>
+  </si>
+  <si>
+    <t>Extra Large</t>
+  </si>
+  <si>
+    <t>Notebook_icf</t>
+  </si>
+  <si>
+    <t>Steel ruler stainless steel</t>
+  </si>
+  <si>
+    <t>30 cm</t>
+  </si>
+  <si>
     <t>Stock Status</t>
   </si>
   <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>01/06/2026 09:01</t>
-  </si>
-  <si>
-    <t>Printixer.ph</t>
-  </si>
-  <si>
-    <t>12-in-1 Multifunctional Paper Cutter</t>
-  </si>
-  <si>
-    <t>Pink</t>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>2025-12-13</t>
+  </si>
+  <si>
+    <t>JTAD.PH (PHOTOLOCK INC.)</t>
+  </si>
+  <si>
+    <t>11oz Blank Sublimation Coated Mug Coffee</t>
+  </si>
+  <si>
+    <t>24pcs/1box</t>
+  </si>
+  <si>
+    <t>Out of Stock</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>Astro Philippines</t>
+  </si>
+  <si>
+    <t>11oz Blank Sublimation Frosted Mug Coffee</t>
+  </si>
+  <si>
+    <t>Plain</t>
   </si>
   <si>
     <t>In Stock</t>
   </si>
   <si>
-    <t>10/10/2025 20:17</t>
-  </si>
-  <si>
-    <t>notebook for school</t>
-  </si>
-  <si>
-    <t>13pcs set NFS Metal Handle With Blades Knife Carving Tools</t>
-  </si>
-  <si>
-    <t>Tool</t>
-  </si>
-  <si>
-    <t>10/10/2025 10:51</t>
-  </si>
-  <si>
-    <t>Digiprint Connection</t>
-  </si>
-  <si>
-    <t>2-in-1 Multi-Function Paper Cutter with scoring board</t>
-  </si>
-  <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t>03/19/2026 09:29</t>
-  </si>
-  <si>
-    <t>LumenLines</t>
-  </si>
-  <si>
-    <t>360 Rotation Heavy Duty Stapler</t>
-  </si>
-  <si>
-    <t>12/20/2025 13:14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPAL </t>
-  </si>
-  <si>
-    <t>3-Layer 18/30 Slots Storage Box</t>
-  </si>
-  <si>
-    <t>18-Grid</t>
-  </si>
-  <si>
-    <t>10/10/2025 10:47</t>
-  </si>
-  <si>
-    <t>Deli Tools Official Store</t>
-  </si>
-  <si>
-    <t>5'' Sharp Mini Diagonal Side Cutting Pliers</t>
-  </si>
-  <si>
-    <t>6 Hole Puncher</t>
-  </si>
-  <si>
-    <t>6 mm</t>
-  </si>
-  <si>
-    <t>11/11/2025 17:09</t>
-  </si>
-  <si>
-    <t>Lalaka</t>
-  </si>
-  <si>
-    <t>6 Layer Metal Rack Steel Rack Shelf</t>
-  </si>
-  <si>
-    <t>100×40×120</t>
-  </si>
-  <si>
-    <t>12/11/2025 20:59</t>
-  </si>
-  <si>
-    <t>Creative Express</t>
-  </si>
-  <si>
-    <t>Automatic Mug Heat Press Machine</t>
-  </si>
-  <si>
-    <t>Blue</t>
-  </si>
-  <si>
-    <t>03/20/2026 18:32</t>
-  </si>
-  <si>
-    <t>GadgetGo</t>
-  </si>
-  <si>
-    <t>Automatic Paper Shredder 8 Sheets Electric Cutter</t>
-  </si>
-  <si>
-    <t>7L</t>
-  </si>
-  <si>
-    <t>Shyvana.ph</t>
-  </si>
-  <si>
-    <t>Bone Folder Craft Tools</t>
-  </si>
-  <si>
-    <t>ADJ Digiprintz Custom</t>
-  </si>
-  <si>
-    <t>Book Binding Tool Starter Kit</t>
-  </si>
-  <si>
-    <t>11/12/2025 21:37</t>
-  </si>
-  <si>
-    <t>wclgdku74i</t>
-  </si>
-  <si>
-    <t>Book Press</t>
-  </si>
-  <si>
-    <t>20*30</t>
-  </si>
-  <si>
-    <t>gardendirect</t>
-  </si>
-  <si>
-    <t>Bookbinding Cover Tool 5 in 1 Book Cover Guide</t>
-  </si>
-  <si>
-    <t>12/20/2025 13:22</t>
-  </si>
-  <si>
-    <t>Crystal Image</t>
-  </si>
-  <si>
-    <t>Brayer Roller</t>
-  </si>
-  <si>
-    <t>White</t>
-  </si>
-  <si>
-    <t>10/24/2025 08:58</t>
-  </si>
-  <si>
-    <t>GRD UNDERGROUND</t>
-  </si>
-  <si>
-    <t>Calendar Clipping Machine</t>
-  </si>
-  <si>
-    <t>Black</t>
-  </si>
-  <si>
-    <t>01/24/2026 21:28</t>
-  </si>
-  <si>
-    <t>Bee Happy Crafts</t>
-  </si>
-  <si>
-    <t>Cinch V2</t>
-  </si>
-  <si>
-    <t>White Pink</t>
-  </si>
-  <si>
-    <t>Dragons Hardware</t>
-  </si>
-  <si>
-    <t>Clamp Clip</t>
-  </si>
-  <si>
-    <t>10/18/2025 08:02</t>
-  </si>
-  <si>
-    <t>dbcraftystation</t>
-  </si>
-  <si>
-    <t>Teal Blue</t>
-  </si>
-  <si>
-    <t>Yasen</t>
-  </si>
-  <si>
-    <t>Corner Rounder R4/R7/R10 3in1 Corner Puncher</t>
-  </si>
-  <si>
-    <t>Craft Weeding Tool Kit</t>
-  </si>
-  <si>
-    <t>12/12/2025 13:10</t>
-  </si>
-  <si>
-    <t>cricut</t>
-  </si>
-  <si>
-    <t>Cricut Explore 4</t>
-  </si>
-  <si>
-    <t>01/17/2026 13:04</t>
-  </si>
-  <si>
-    <t>Cricut Explore Deep Point Blade/Deep Cut Blade</t>
-  </si>
-  <si>
-    <t>Thick Materials</t>
-  </si>
-  <si>
-    <t>daphne.home.ph</t>
-  </si>
-  <si>
-    <t>Cricut Explore Padded Dust Cover</t>
-  </si>
-  <si>
-    <t>01/17/2026 13:05</t>
-  </si>
-  <si>
-    <t>Googlygooeys 3D Cricut Crafts</t>
-  </si>
-  <si>
-    <t>Cutting Mat for Cricut</t>
-  </si>
-  <si>
-    <t>Lilac Strong 12x12</t>
-  </si>
-  <si>
-    <t>12/12/2025 13:16</t>
-  </si>
-  <si>
-    <t>ANT HOME</t>
-  </si>
-  <si>
-    <t>Detachable Tool Kit DIY Leather Sewing</t>
-  </si>
-  <si>
-    <t>12/23/2025 17:11</t>
-  </si>
-  <si>
-    <t>Concon.InkShop</t>
-  </si>
-  <si>
-    <t>Epson Printer L121</t>
-  </si>
-  <si>
-    <t>Sublimation</t>
-  </si>
-  <si>
-    <t>03/03/2026 09:47</t>
-  </si>
-  <si>
-    <t>arlenemamadel online shop</t>
-  </si>
-  <si>
-    <t>Epson Printer L121 Dust Cover</t>
-  </si>
-  <si>
-    <t>EasyBuy Mall</t>
-  </si>
-  <si>
-    <t>Eyelet Plier Set Hole Punch</t>
-  </si>
-  <si>
-    <t>Hole Puncher Circle</t>
-  </si>
-  <si>
-    <t>Far Eastern Hardware</t>
-  </si>
-  <si>
-    <t>INGCO Scissors Stainless Steel</t>
-  </si>
-  <si>
-    <t>11"</t>
-  </si>
-  <si>
-    <t>cafe.ph ( photolock.inc)</t>
-  </si>
-  <si>
-    <t>Laminator Machine</t>
-  </si>
-  <si>
-    <t>A3/A4</t>
-  </si>
-  <si>
-    <t>Min Shop</t>
-  </si>
-  <si>
-    <t>Long arm heavy duty Stapler</t>
-  </si>
-  <si>
-    <t>Vientiane</t>
-  </si>
-  <si>
-    <t>Mini Heat Press Machine for T Shirts Portable</t>
-  </si>
-  <si>
-    <t>12/27/2025 16:57</t>
-  </si>
-  <si>
-    <t>rules.ph</t>
-  </si>
-  <si>
-    <t>Multiple Layers Desktop Printer Stand</t>
-  </si>
-  <si>
-    <t>2 Tier White</t>
-  </si>
-  <si>
-    <t>YAMIGO Philippines</t>
-  </si>
-  <si>
-    <t>Multi-Purpose Envelope Punch Board</t>
-  </si>
-  <si>
-    <t>10/18/2025 08:01</t>
-  </si>
-  <si>
-    <t>Officom Hot Melt Binding Machine</t>
-  </si>
-  <si>
-    <t>50 mm</t>
-  </si>
-  <si>
-    <t>Officom Paper Cutter Metal</t>
-  </si>
-  <si>
-    <t>B3: 35.3cm x 50cm</t>
-  </si>
-  <si>
-    <t>10/10/2025 10:26</t>
-  </si>
-  <si>
-    <t>Officom Ream Cutter</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>Douwells Arts and Crafts</t>
-  </si>
-  <si>
-    <t>Paper Punch Loose Leaf Hole Puncher</t>
-  </si>
-  <si>
-    <t>30 Holes</t>
-  </si>
-  <si>
-    <t>Louisfashion</t>
-  </si>
-  <si>
-    <t>Patchwork Ruler Quilting Acrylic</t>
-  </si>
-  <si>
-    <t>30*15</t>
-  </si>
-  <si>
-    <t>PVC Cutting Mat A3 A4 A5 elf-Healing Pad Cutting Board</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>10/31/2025 19:56</t>
-  </si>
-  <si>
-    <t>creativenest</t>
-  </si>
-  <si>
-    <t>Ream Cutter Cutting Guide</t>
-  </si>
-  <si>
-    <t>A5 &amp; A6</t>
-  </si>
-  <si>
-    <t>Knotjustcraft Online Shop</t>
-  </si>
-  <si>
-    <t>Squeegee Promax for Decal, Stickers, Phototop Application</t>
-  </si>
-  <si>
-    <t>Extra Large</t>
-  </si>
-  <si>
-    <t>Notebook_icf</t>
-  </si>
-  <si>
-    <t>Steel ruler stainless steel</t>
-  </si>
-  <si>
-    <t>30 cm</t>
-  </si>
-  <si>
-    <t>Material</t>
-  </si>
-  <si>
-    <t>12/13/2025 21:25</t>
-  </si>
-  <si>
-    <t>JTAD.PH (PHOTOLOCK INC.)</t>
-  </si>
-  <si>
-    <t>11oz Blank Sublimation Coated Mug Coffee</t>
-  </si>
-  <si>
-    <t>24pcs/1box</t>
-  </si>
-  <si>
-    <t>03/17/2026 07:59</t>
-  </si>
-  <si>
-    <t>Astro Philippines</t>
-  </si>
-  <si>
-    <t>11oz Blank Sublimation Frosted Mug Coffee</t>
-  </si>
-  <si>
-    <t>Plain</t>
-  </si>
-  <si>
     <t>Lemon Yellow</t>
   </si>
   <si>
@@ -523,7 +498,7 @@
     <t>Rose Gold, 1"</t>
   </si>
   <si>
-    <t>10/13/2025 22:06</t>
+    <t>2025-10-13</t>
   </si>
   <si>
     <t>All Toner Ink Hub</t>
@@ -535,16 +510,13 @@
     <t>Short, 80gsm</t>
   </si>
   <si>
-    <t>10/10/2025 10:33</t>
-  </si>
-  <si>
     <t>A4, 80gsm</t>
   </si>
   <si>
     <t>A4, 100gsm</t>
   </si>
   <si>
-    <t>12/09/2025 14:19</t>
+    <t>2025-12-09</t>
   </si>
   <si>
     <t>judessashop</t>
@@ -565,9 +537,6 @@
     <t>58mm</t>
   </si>
   <si>
-    <t>01/24/2026 20:57</t>
-  </si>
-  <si>
     <t>kaituozhe.ph</t>
   </si>
   <si>
@@ -583,7 +552,7 @@
     <t>Flat, 12mm</t>
   </si>
   <si>
-    <t>12/04/2025 09:09</t>
+    <t>2025-12-04</t>
   </si>
   <si>
     <t>littleguymyie.ph</t>
@@ -595,7 +564,7 @@
     <t>C,M,Y,K+BK (4 free 1)</t>
   </si>
   <si>
-    <t>12/05/2025 11:48</t>
+    <t>2025-12-05</t>
   </si>
   <si>
     <t>GP-Print</t>
@@ -616,9 +585,6 @@
     <t>Peach, 18*23</t>
   </si>
   <si>
-    <t>10/31/2025 20:07</t>
-  </si>
-  <si>
     <t>MamaCraftsStore</t>
   </si>
   <si>
@@ -631,7 +597,7 @@
     <t>A5, 330gsm Landscape</t>
   </si>
   <si>
-    <t>11/15/2025 12:45</t>
+    <t>2025-11-15</t>
   </si>
   <si>
     <t>S Binding Supplies, Inc.</t>
@@ -646,9 +612,6 @@
     <t>Black, 8-7/8"</t>
   </si>
   <si>
-    <t>10/24/2025 08:59</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gabryn &amp; Gereign Online Store </t>
   </si>
   <si>
@@ -658,9 +621,6 @@
     <t>8.3"</t>
   </si>
   <si>
-    <t>10/10/2025 10:31</t>
-  </si>
-  <si>
     <t>Quaff Philippines</t>
   </si>
   <si>
@@ -670,7 +630,7 @@
     <t>A4, Matte, 250gsm</t>
   </si>
   <si>
-    <t>03/14/2026 06:34</t>
+    <t>2026-03-14</t>
   </si>
   <si>
     <t>PH_office4U</t>
@@ -694,16 +654,13 @@
     <t>E2 22*15/3x4cm</t>
   </si>
   <si>
-    <t>10/31/2025 20:08</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tbox </t>
   </si>
   <si>
     <t>T4 25*20.5*7cm</t>
   </si>
   <si>
-    <t>12/06/2025 16:23</t>
+    <t>2025-12-06</t>
   </si>
   <si>
     <t>T2 6*6*2’‘</t>
@@ -721,7 +678,7 @@
     <t>A4, #50</t>
   </si>
   <si>
-    <t>10/12/2025 20:16</t>
+    <t>2025-10-12</t>
   </si>
   <si>
     <t>A4, #40</t>
@@ -733,7 +690,7 @@
     <t>A4, #30</t>
   </si>
   <si>
-    <t>03/15/2026 16:56</t>
+    <t>2026-03-15</t>
   </si>
   <si>
     <t>bnesos</t>
@@ -751,7 +708,7 @@
     <t>A4, Mixed Color</t>
   </si>
   <si>
-    <t>11/13/2025 13:50</t>
+    <t>2025-11-13</t>
   </si>
   <si>
     <t>Double Sided Glossy Photo Paper</t>
@@ -763,19 +720,19 @@
     <t>A4, 250gsm</t>
   </si>
   <si>
-    <t>12/03/2025 15:17</t>
+    <t>2025-12-03</t>
   </si>
   <si>
     <t>A4, 200gsm</t>
   </si>
   <si>
-    <t>11/25/2025 08:53</t>
+    <t>2025-11-25</t>
   </si>
   <si>
     <t>A4, 120gsm</t>
   </si>
   <si>
-    <t>11/07/2025 21:34</t>
+    <t>2025-11-07</t>
   </si>
   <si>
     <t>A4, Glossy, 220gsm</t>
@@ -790,9 +747,6 @@
     <t>12 x 10m</t>
   </si>
   <si>
-    <t>10/13/2025 22:07</t>
-  </si>
-  <si>
     <t>Hunter Hardware</t>
   </si>
   <si>
@@ -811,16 +765,13 @@
     <t>E7000</t>
   </si>
   <si>
-    <t>12/23/2025 08:51</t>
-  </si>
-  <si>
     <t>Shopee Choice Global</t>
   </si>
   <si>
     <t>B7000</t>
   </si>
   <si>
-    <t>01/13/2026 20:10</t>
+    <t>2026-01-13</t>
   </si>
   <si>
     <t>CED CRAFTY CORNER</t>
@@ -844,7 +795,7 @@
     <t>Blue Lagoon, 21 x 30cm</t>
   </si>
   <si>
-    <t>02/02/2026 20:49</t>
+    <t>2026-02-02</t>
   </si>
   <si>
     <t>BuildCore.Tool</t>
@@ -862,9 +813,6 @@
     <t>Fold cote paper</t>
   </si>
   <si>
-    <t>11/15/2025 12:42</t>
-  </si>
-  <si>
     <t>Crafters Corner &amp; Supplies</t>
   </si>
   <si>
@@ -880,9 +828,6 @@
     <t>6 colors</t>
   </si>
   <si>
-    <t>03/15/2026 08:05</t>
-  </si>
-  <si>
     <t>Lil'love Baby</t>
   </si>
   <si>
@@ -910,7 +855,7 @@
     <t>Hexagon</t>
   </si>
   <si>
-    <t>10/15/2025 20:48</t>
+    <t>2025-10-15</t>
   </si>
   <si>
     <t>&amp;Frontline&amp;</t>
@@ -931,33 +876,24 @@
     <t>Hot Melt Glue Strips</t>
   </si>
   <si>
-    <t>10/24/2025 08:57</t>
-  </si>
-  <si>
     <t>3mm</t>
   </si>
   <si>
     <t>2mm</t>
   </si>
   <si>
-    <t>11/13/2025 13:55</t>
-  </si>
-  <si>
     <t>Inkjet Photo Sticker</t>
   </si>
   <si>
     <t>A3, Glossy, 135gsm</t>
   </si>
   <si>
-    <t>11/29/2025 09:56</t>
+    <t>2025-11-29</t>
   </si>
   <si>
     <t>A4, Matte, 135gsm</t>
   </si>
   <si>
-    <t>11/07/2025 13:35</t>
-  </si>
-  <si>
     <t>A4, Glossy, 135gsm</t>
   </si>
   <si>
@@ -982,9 +918,6 @@
     <t>A3, 300gsm</t>
   </si>
   <si>
-    <t>12/03/2025 09:24</t>
-  </si>
-  <si>
     <t>Laminating Film</t>
   </si>
   <si>
@@ -997,9 +930,6 @@
     <t>A4, Glossy, 125micron</t>
   </si>
   <si>
-    <t>12/13/2025 21:15</t>
-  </si>
-  <si>
     <t>Manila Gift Shop</t>
   </si>
   <si>
@@ -1033,9 +963,6 @@
     <t>White Diamond</t>
   </si>
   <si>
-    <t>01/13/2026 20:26</t>
-  </si>
-  <si>
     <t>JD.PH</t>
   </si>
   <si>
@@ -1045,7 +972,7 @@
     <t>Gold, 831</t>
   </si>
   <si>
-    <t>11/22/2025 15:51</t>
+    <t>2025-11-22</t>
   </si>
   <si>
     <t>Loona Creates</t>
@@ -1066,7 +993,7 @@
     <t>831</t>
   </si>
   <si>
-    <t>02/07/2026 22:31</t>
+    <t>2026-02-07</t>
   </si>
   <si>
     <t>TwistedColors</t>
@@ -1087,9 +1014,6 @@
     <t>Long, 42gsm</t>
   </si>
   <si>
-    <t>01/06/2026 09:05</t>
-  </si>
-  <si>
     <t>XM01 ONLINE STORE</t>
   </si>
   <si>
@@ -1105,7 +1029,7 @@
     <t>White, 12.7mm</t>
   </si>
   <si>
-    <t>12/02/2025 10:19</t>
+    <t>2025-12-02</t>
   </si>
   <si>
     <t>Kenyan Office Supplies</t>
@@ -1114,7 +1038,7 @@
     <t>Rose Gold, 12.7mm</t>
   </si>
   <si>
-    <t>10/20/2025 17:17</t>
+    <t>2025-10-20</t>
   </si>
   <si>
     <t>Rose, 12.7mm</t>
@@ -1129,9 +1053,6 @@
     <t>Golden, 14.3mm</t>
   </si>
   <si>
-    <t>10/20/2025 17:16</t>
-  </si>
-  <si>
     <t>Black, 14.3mm</t>
   </si>
   <si>
@@ -1159,7 +1080,7 @@
     <t>8.5 x 10"</t>
   </si>
   <si>
-    <t>12/15/2025 09:58</t>
+    <t>2025-12-15</t>
   </si>
   <si>
     <t>Whimsical gift shop</t>
@@ -1168,9 +1089,6 @@
     <t>6 × 9.6"</t>
   </si>
   <si>
-    <t>11/25/2025 20:48</t>
-  </si>
-  <si>
     <t>Andojar Packaging Supplies</t>
   </si>
   <si>
@@ -1204,7 +1122,7 @@
     <t>Small</t>
   </si>
   <si>
-    <t>12/01/2025 10:23</t>
+    <t>2025-12-01</t>
   </si>
   <si>
     <t>Photo Top Cold Laminating Film A4 Size</t>
@@ -1228,16 +1146,13 @@
     <t>Glitter</t>
   </si>
   <si>
-    <t>12/13/2025 20:24</t>
-  </si>
-  <si>
     <t>W.Starry</t>
   </si>
   <si>
     <t>Pocket mirror Badge Button</t>
   </si>
   <si>
-    <t>03/10/2026 10:04</t>
+    <t>2026-03-10</t>
   </si>
   <si>
     <t>Office Supplies MNL</t>
@@ -1249,9 +1164,6 @@
     <t>A4, without hole</t>
   </si>
   <si>
-    <t>12/11/2025 08:46</t>
-  </si>
-  <si>
     <t>InfinityKrafts</t>
   </si>
   <si>
@@ -1267,9 +1179,6 @@
     <t>Set Book binding Mull Cloth</t>
   </si>
   <si>
-    <t>12/23/2025 08:52</t>
-  </si>
-  <si>
     <t>ZNB Digital</t>
   </si>
   <si>
@@ -1285,9 +1194,6 @@
     <t>A4, 2mm</t>
   </si>
   <si>
-    <t>10/24/2025 16:41</t>
-  </si>
-  <si>
     <t>coilcenter</t>
   </si>
   <si>
@@ -1297,9 +1203,6 @@
     <t>Black, 42mm</t>
   </si>
   <si>
-    <t>10/24/2025 16:38</t>
-  </si>
-  <si>
     <t>Clear, 22mm</t>
   </si>
   <si>
@@ -1315,7 +1218,7 @@
     <t>Black, 8mm</t>
   </si>
   <si>
-    <t>12/30/2025 16:31</t>
+    <t>2025-12-30</t>
   </si>
   <si>
     <t>Sublimation Paper</t>
@@ -1334,9 +1237,6 @@
   </si>
   <si>
     <t>Gold Pink, 300ml</t>
-  </si>
-  <si>
-    <t>Out of Stock</t>
   </si>
   <si>
     <t>Vellum Board Paper</t>
@@ -1726,7 +1626,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4250DEE6-476E-4522-9FB2-342A0A91348D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1764,19 +1664,19 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
       </c>
       <c r="F2" s="3">
         <v>1</v>
@@ -1787,19 +1687,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
       </c>
       <c r="F3" s="3">
         <v>1</v>
@@ -1810,19 +1710,19 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
       </c>
       <c r="F4" s="3">
         <v>1</v>
@@ -1833,19 +1733,19 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1856,19 +1756,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
         <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
       </c>
       <c r="F6" s="3">
         <v>1</v>
@@ -1879,19 +1779,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
@@ -1902,19 +1802,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F8" s="3">
         <v>1</v>
@@ -1925,19 +1825,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F9" s="3">
         <v>1</v>
@@ -1948,19 +1848,19 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F10" s="3">
         <v>1</v>
@@ -1971,19 +1871,19 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F11" s="3">
         <v>1</v>
@@ -1994,19 +1894,19 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F12" s="3">
         <v>1</v>
@@ -2017,19 +1917,19 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F13" s="3">
         <v>1</v>
@@ -2040,19 +1940,19 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F14" s="3">
         <v>1</v>
@@ -2063,19 +1963,19 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F15" s="3">
         <v>1</v>
@@ -2086,19 +1986,19 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
@@ -2109,19 +2009,19 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
@@ -2132,19 +2032,19 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E18" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F18" s="3">
         <v>1</v>
@@ -2155,19 +2055,19 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F19" s="3">
         <v>3</v>
@@ -2178,19 +2078,19 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F20" s="3">
         <v>1</v>
@@ -2201,19 +2101,19 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F21" s="3">
         <v>1</v>
@@ -2224,19 +2124,19 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F22" s="3">
         <v>1</v>
@@ -2247,19 +2147,19 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E23" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F23" s="3">
         <v>1</v>
@@ -2270,19 +2170,19 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E24" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F24" s="3">
         <v>1</v>
@@ -2293,19 +2193,19 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E25" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F25" s="3">
         <v>1</v>
@@ -2316,19 +2216,19 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E26" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F26" s="3">
         <v>1</v>
@@ -2339,19 +2239,19 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F27" s="3">
         <v>1</v>
@@ -2362,19 +2262,19 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D28" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E28" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F28" s="3">
         <v>1</v>
@@ -2385,19 +2285,19 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E29" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F29" s="3">
         <v>1</v>
@@ -2408,19 +2308,19 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F30" s="3">
         <v>1</v>
@@ -2431,19 +2331,19 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D31" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F31" s="3">
         <v>1</v>
@@ -2454,19 +2354,19 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D32" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E32" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
@@ -2477,19 +2377,19 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E33" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F33" s="3">
         <v>1</v>
@@ -2500,19 +2400,19 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D34" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F34" s="3">
         <v>1</v>
@@ -2523,19 +2423,19 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D35" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F35" s="3">
         <v>1</v>
@@ -2546,19 +2446,19 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E36" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F36" s="3">
         <v>1</v>
@@ -2569,19 +2469,19 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C37" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F37" s="3">
         <v>1</v>
@@ -2592,19 +2492,19 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D38" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E38" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F38" s="3">
         <v>1</v>
@@ -2615,19 +2515,19 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D39" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E39" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F39" s="3">
         <v>1</v>
@@ -2638,19 +2538,19 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>122</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E40" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="F40" s="3">
         <v>1</v>
@@ -2661,19 +2561,19 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B41" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" t="s">
+        <v>116</v>
+      </c>
+      <c r="D41" t="s">
         <v>117</v>
       </c>
-      <c r="C41" t="s">
-        <v>125</v>
-      </c>
-      <c r="D41" t="s">
-        <v>126</v>
-      </c>
       <c r="E41" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="F41" s="3">
         <v>1</v>
@@ -2684,19 +2584,19 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D42" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E42" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="F42" s="3">
         <v>1</v>
@@ -2707,19 +2607,19 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D43" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E43" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F43" s="3">
         <v>1</v>
@@ -2730,19 +2630,19 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C44" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D44" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E44" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="F44" s="3">
         <v>1</v>
@@ -2753,19 +2653,19 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D45" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E45" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="F45" s="3">
         <v>1</v>
@@ -2776,19 +2676,19 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C46" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D46" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E46" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="F46" s="3">
         <v>1</v>
@@ -2799,13 +2699,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{262D17EA-A989-4A54-B60C-4F7CA01CB541}">
-  <dimension ref="A1:H149"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:K149"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2816,6 +2716,7 @@
     <col min="6" max="6" width="11.77734375" style="3" customWidth="1"/>
     <col min="7" max="7" width="15" style="4" customWidth="1"/>
     <col min="8" max="8" width="17.109375" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -2841,24 +2742,24 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>7</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F2" s="3">
         <v>24</v>
@@ -2867,24 +2768,24 @@
         <v>684</v>
       </c>
       <c r="H2" t="s">
-        <v>431</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" t="s">
         <v>143</v>
       </c>
-      <c r="B3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D3" t="s">
-        <v>150</v>
-      </c>
       <c r="E3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F3" s="3">
         <v>1</v>
@@ -2893,24 +2794,24 @@
         <v>67</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" t="s">
         <v>143</v>
       </c>
-      <c r="B4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" t="s">
-        <v>150</v>
-      </c>
       <c r="E4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F4" s="3">
         <v>1</v>
@@ -2919,24 +2820,24 @@
         <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" t="s">
         <v>143</v>
       </c>
-      <c r="B5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D5" t="s">
-        <v>150</v>
-      </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -2945,24 +2846,24 @@
         <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F6" s="3">
         <v>5</v>
@@ -2971,24 +2872,24 @@
         <v>33</v>
       </c>
       <c r="H6" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F7" s="3">
         <v>5</v>
@@ -2997,24 +2898,24 @@
         <v>33</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F8" s="3">
         <v>5</v>
@@ -3023,24 +2924,24 @@
         <v>33</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D9" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F9" s="3">
         <v>5</v>
@@ -3049,24 +2950,24 @@
         <v>33</v>
       </c>
       <c r="H9" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" s="3">
         <v>5</v>
@@ -3075,24 +2976,24 @@
         <v>33</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E11" t="s">
         <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" t="s">
-        <v>21</v>
       </c>
       <c r="F11" s="3">
         <v>5</v>
@@ -3101,24 +3002,24 @@
         <v>38</v>
       </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E12" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F12" s="3">
         <v>10</v>
@@ -3127,24 +3028,24 @@
         <v>273</v>
       </c>
       <c r="H12" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B13" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E13" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="F13" s="3">
         <v>500</v>
@@ -3153,24 +3054,24 @@
         <v>238</v>
       </c>
       <c r="H13" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B14" t="s">
-        <v>164</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E14" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F14" s="3">
         <v>500</v>
@@ -3179,24 +3080,24 @@
         <v>263</v>
       </c>
       <c r="H14" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B15" t="s">
-        <v>164</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D15" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E15" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F15" s="3">
         <v>500</v>
@@ -3205,24 +3106,24 @@
         <v>355</v>
       </c>
       <c r="H15" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C16" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D16" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E16" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
@@ -3231,24 +3132,24 @@
         <v>22</v>
       </c>
       <c r="H16" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E17" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F17" s="3">
         <v>50</v>
@@ -3257,24 +3158,24 @@
         <v>503</v>
       </c>
       <c r="H17" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s">
-        <v>174</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D18" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="E18" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="F18" s="3">
         <v>20</v>
@@ -3283,24 +3184,24 @@
         <v>132</v>
       </c>
       <c r="H18" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D19" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="E19" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F19" s="3">
         <v>20</v>
@@ -3309,24 +3210,24 @@
         <v>115</v>
       </c>
       <c r="H19" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D20" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="E20" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="F20" s="3">
         <v>20</v>
@@ -3335,24 +3236,24 @@
         <v>142</v>
       </c>
       <c r="H20" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D21" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E21" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F21" s="3">
         <v>1</v>
@@ -3361,24 +3262,24 @@
         <v>732</v>
       </c>
       <c r="H21" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B22" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C22" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D22" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E22" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="F22" s="3">
         <v>1</v>
@@ -3387,24 +3288,24 @@
         <v>239</v>
       </c>
       <c r="H22" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D23" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E23" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="F23" s="3">
         <v>1</v>
@@ -3413,24 +3314,24 @@
         <v>212</v>
       </c>
       <c r="H23" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D24" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E24" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F24" s="3">
         <v>1</v>
@@ -3439,24 +3340,24 @@
         <v>212</v>
       </c>
       <c r="H24" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D25" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E25" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F25" s="3">
         <v>1</v>
@@ -3465,24 +3366,24 @@
         <v>213</v>
       </c>
       <c r="H25" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B26" t="s">
-        <v>164</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D26" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="E26" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F26" s="3">
         <v>10</v>
@@ -3491,24 +3392,24 @@
         <v>76</v>
       </c>
       <c r="H26" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B27" t="s">
-        <v>191</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D27" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="E27" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F27" s="3">
         <v>25</v>
@@ -3517,24 +3418,24 @@
         <v>106</v>
       </c>
       <c r="H27" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B28" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C28" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D28" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="E28" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F28" s="3">
         <v>25</v>
@@ -3543,24 +3444,24 @@
         <v>169</v>
       </c>
       <c r="H28" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B29" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C29" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D29" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E29" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="F29" s="3">
         <v>20</v>
@@ -3569,24 +3470,24 @@
         <v>83</v>
       </c>
       <c r="H29" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B30" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C30" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D30" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E30" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="F30" s="3">
         <v>20</v>
@@ -3595,24 +3496,24 @@
         <v>102</v>
       </c>
       <c r="H30" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B31" t="s">
-        <v>201</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="D31" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="E31" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="F31" s="3">
         <v>50</v>
@@ -3621,24 +3522,24 @@
         <v>150</v>
       </c>
       <c r="H31" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B32" t="s">
-        <v>205</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D32" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="E32" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="F32" s="3">
         <v>50</v>
@@ -3647,24 +3548,24 @@
         <v>99</v>
       </c>
       <c r="H32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B33" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C33" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D33" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="E33" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="F33" s="3">
         <v>1</v>
@@ -3673,24 +3574,24 @@
         <v>132</v>
       </c>
       <c r="H33" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B34" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C34" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D34" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="E34" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F34" s="3">
         <v>1</v>
@@ -3699,24 +3600,24 @@
         <v>132</v>
       </c>
       <c r="H34" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B35" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C35" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D35" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="E35" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F35" s="3">
         <v>1</v>
@@ -3725,24 +3626,24 @@
         <v>131</v>
       </c>
       <c r="H35" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B36" t="s">
-        <v>191</v>
+        <v>124</v>
       </c>
       <c r="C36" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="D36" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="E36" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="F36" s="3">
         <v>10</v>
@@ -3751,24 +3652,24 @@
         <v>189</v>
       </c>
       <c r="H36" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C37" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="D37" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="E37" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F37" s="3">
         <v>10</v>
@@ -3777,24 +3678,24 @@
         <v>68</v>
       </c>
       <c r="H37" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B38" t="s">
-        <v>217</v>
+        <v>124</v>
       </c>
       <c r="C38" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="D38" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="E38" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="F38" s="3">
         <v>5</v>
@@ -3803,24 +3704,25 @@
         <v>85</v>
       </c>
       <c r="H38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+      <c r="K38" s="4"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B39" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C39" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="D39" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="E39" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="F39" s="3">
         <v>5</v>
@@ -3829,24 +3731,24 @@
         <v>40</v>
       </c>
       <c r="H39" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B40" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C40" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="D40" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="E40" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F40" s="3">
         <v>5</v>
@@ -3855,24 +3757,24 @@
         <v>55</v>
       </c>
       <c r="H40" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B41" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C41" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D41" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="E41" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F41" s="3">
         <v>100</v>
@@ -3881,24 +3783,24 @@
         <v>800</v>
       </c>
       <c r="H41" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B42" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="C42" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D42" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="E42" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F42" s="3">
         <v>25</v>
@@ -3907,24 +3809,24 @@
         <v>160</v>
       </c>
       <c r="H42" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B43" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="C43" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D43" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="E43" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F43" s="3">
         <v>25</v>
@@ -3933,24 +3835,24 @@
         <v>200</v>
       </c>
       <c r="H43" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D44" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="E44" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F44" s="3">
         <v>25</v>
@@ -3959,24 +3861,24 @@
         <v>150.5</v>
       </c>
       <c r="H44" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D45" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="E45" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F45" s="3">
         <v>25</v>
@@ -3985,24 +3887,24 @@
         <v>205.5</v>
       </c>
       <c r="H45" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B46" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="C46" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="D46" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="E46" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="F46" s="3">
         <v>35</v>
@@ -4011,24 +3913,24 @@
         <v>154</v>
       </c>
       <c r="H46" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B47" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C47" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="D47" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="E47" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="F47" s="3">
         <v>20</v>
@@ -4037,24 +3939,24 @@
         <v>60</v>
       </c>
       <c r="H47" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B48" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="C48" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D48" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="E48" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="F48" s="3">
         <v>50</v>
@@ -4063,24 +3965,24 @@
         <v>285</v>
       </c>
       <c r="H48" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B49" t="s">
-        <v>174</v>
+        <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D49" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="E49" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="F49" s="3">
         <v>50</v>
@@ -4089,24 +3991,24 @@
         <v>140</v>
       </c>
       <c r="H49" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B50" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C50" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D50" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="E50" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F50" s="3">
         <v>200</v>
@@ -4115,24 +4017,24 @@
         <v>432</v>
       </c>
       <c r="H50" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B51" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="C51" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D51" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="E51" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F51" s="3">
         <v>250</v>
@@ -4141,24 +4043,24 @@
         <v>590</v>
       </c>
       <c r="H51" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C52" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D52" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="E52" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F52" s="3">
         <v>500</v>
@@ -4167,24 +4069,24 @@
         <v>1047</v>
       </c>
       <c r="H52" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B53" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="C53" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D53" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="E53" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F53" s="3">
         <v>100</v>
@@ -4193,24 +4095,24 @@
         <v>252</v>
       </c>
       <c r="H53" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B54" t="s">
-        <v>205</v>
+        <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D54" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="E54" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F54" s="3">
         <v>50</v>
@@ -4219,24 +4121,24 @@
         <v>102</v>
       </c>
       <c r="H54" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B55" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D55" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E55" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="F55" s="3">
         <v>2</v>
@@ -4245,24 +4147,24 @@
         <v>70</v>
       </c>
       <c r="H55" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B56" t="s">
-        <v>249</v>
+        <v>154</v>
       </c>
       <c r="C56" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="D56" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="E56" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="F56" s="3">
         <v>1</v>
@@ -4271,24 +4173,24 @@
         <v>46</v>
       </c>
       <c r="H56" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B57" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C57" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="D57" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="E57" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F57" s="3">
         <v>1</v>
@@ -4297,24 +4199,24 @@
         <v>61</v>
       </c>
       <c r="H57" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>256</v>
+        <v>84</v>
       </c>
       <c r="C58" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D58" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="E58" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F58" s="3">
         <v>1</v>
@@ -4323,24 +4225,24 @@
         <v>37</v>
       </c>
       <c r="H58" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B59" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="C59" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="D59" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="E59" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F59" s="3">
         <v>1</v>
@@ -4349,24 +4251,24 @@
         <v>90</v>
       </c>
       <c r="H59" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B60" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="C60" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="D60" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="E60" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="F60" s="3">
         <v>1</v>
@@ -4375,24 +4277,24 @@
         <v>90</v>
       </c>
       <c r="H60" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B61" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="C61" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="D61" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="E61" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="F61" s="3">
         <v>1</v>
@@ -4401,24 +4303,24 @@
         <v>90</v>
       </c>
       <c r="H61" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C62" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D62" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="E62" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="F62" s="3">
         <v>1</v>
@@ -4427,24 +4329,24 @@
         <v>40</v>
       </c>
       <c r="H62" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C63" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D63" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="E63" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="F63" s="3">
         <v>1</v>
@@ -4453,24 +4355,24 @@
         <v>50</v>
       </c>
       <c r="H63" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B64" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="C64" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="D64" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="E64" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="F64" s="3">
         <v>1</v>
@@ -4479,24 +4381,24 @@
         <v>28</v>
       </c>
       <c r="H64" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B65" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="D65" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="E65" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="F65" s="3">
         <v>25</v>
@@ -4505,24 +4407,24 @@
         <v>204</v>
       </c>
       <c r="H65" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B66" t="s">
-        <v>273</v>
+        <v>187</v>
       </c>
       <c r="C66" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="D66" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="E66" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="F66" s="3">
         <v>25</v>
@@ -4531,24 +4433,24 @@
         <v>184</v>
       </c>
       <c r="H66" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B67" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C67" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="E67" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="F67" s="3">
         <v>35</v>
@@ -4557,24 +4459,24 @@
         <v>205</v>
       </c>
       <c r="H67" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B68" t="s">
-        <v>279</v>
+        <v>218</v>
       </c>
       <c r="C68" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="D68" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="E68" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="F68" s="3">
         <v>8</v>
@@ -4583,24 +4485,24 @@
         <v>200</v>
       </c>
       <c r="H68" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B69" t="s">
-        <v>279</v>
+        <v>218</v>
       </c>
       <c r="C69" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="D69" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="E69" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F69" s="3">
         <v>2</v>
@@ -4609,24 +4511,24 @@
         <v>94</v>
       </c>
       <c r="H69" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B70" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C70" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D70" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="E70" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="F70" s="3">
         <v>1</v>
@@ -4635,24 +4537,24 @@
         <v>7</v>
       </c>
       <c r="H70" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B71" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C71" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="D71" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="E71" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="F71" s="3">
         <v>40</v>
@@ -4661,24 +4563,24 @@
         <v>214</v>
       </c>
       <c r="H71" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B72" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="C72" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="D72" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="E72" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="F72" s="3">
         <v>1</v>
@@ -4687,24 +4589,24 @@
         <v>55</v>
       </c>
       <c r="H72" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B73" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="C73" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="D73" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="E73" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="F73" s="3">
         <v>1</v>
@@ -4713,24 +4615,24 @@
         <v>62</v>
       </c>
       <c r="H73" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B74" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="C74" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="D74" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="E74" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="F74" s="3">
         <v>1</v>
@@ -4739,24 +4641,24 @@
         <v>69</v>
       </c>
       <c r="H74" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B75" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C75" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D75" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="E75" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="F75" s="3">
         <v>10</v>
@@ -4765,24 +4667,24 @@
         <v>97</v>
       </c>
       <c r="H75" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B76" t="s">
-        <v>296</v>
+        <v>55</v>
       </c>
       <c r="C76" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D76" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="E76" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="F76" s="3">
         <v>40</v>
@@ -4791,24 +4693,24 @@
         <v>73.5</v>
       </c>
       <c r="H76" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B77" t="s">
-        <v>296</v>
+        <v>55</v>
       </c>
       <c r="C77" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D77" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="E77" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="F77" s="3">
         <v>200</v>
@@ -4817,24 +4719,24 @@
         <v>453.5</v>
       </c>
       <c r="H77" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B78" t="s">
-        <v>299</v>
+        <v>224</v>
       </c>
       <c r="C78" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D78" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="E78" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="F78" s="3">
         <v>20</v>
@@ -4843,24 +4745,24 @@
         <v>148</v>
       </c>
       <c r="H78" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B79" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="C79" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D79" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="E79" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="F79" s="3">
         <v>200</v>
@@ -4869,24 +4771,24 @@
         <v>574</v>
       </c>
       <c r="H79" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B80" t="s">
-        <v>304</v>
+        <v>232</v>
       </c>
       <c r="C80" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D80" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="E80" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="F80" s="3">
         <v>40</v>
@@ -4895,24 +4797,24 @@
         <v>156</v>
       </c>
       <c r="H80" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B81" t="s">
-        <v>304</v>
+        <v>232</v>
       </c>
       <c r="C81" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D81" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="E81" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="F81" s="3">
         <v>100</v>
@@ -4921,24 +4823,24 @@
         <v>319</v>
       </c>
       <c r="H81" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B82" t="s">
-        <v>205</v>
+        <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D82" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="E82" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="F82" s="3">
         <v>20</v>
@@ -4947,24 +4849,24 @@
         <v>78</v>
       </c>
       <c r="H82" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B83" t="s">
-        <v>205</v>
+        <v>12</v>
       </c>
       <c r="C83" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D83" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="E83" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="F83" s="3">
         <v>20</v>
@@ -4973,24 +4875,24 @@
         <v>78</v>
       </c>
       <c r="H83" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B84" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C84" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="D84" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="E84" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="F84" s="3">
         <v>1</v>
@@ -4999,24 +4901,24 @@
         <v>86</v>
       </c>
       <c r="H84" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B85" t="s">
-        <v>273</v>
+        <v>187</v>
       </c>
       <c r="C85" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="D85" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="E85" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="F85" s="3">
         <v>25</v>
@@ -5025,24 +4927,24 @@
         <v>191</v>
       </c>
       <c r="H85" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B86" t="s">
-        <v>313</v>
+        <v>228</v>
       </c>
       <c r="C86" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D86" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="E86" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="F86" s="3">
         <v>300</v>
@@ -5051,24 +4953,24 @@
         <v>498</v>
       </c>
       <c r="H86" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B87" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="C87" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D87" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="E87" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="F87" s="3">
         <v>100</v>
@@ -5077,24 +4979,24 @@
         <v>149</v>
       </c>
       <c r="H87" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B88" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="C88" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D88" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="E88" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="F88" s="3">
         <v>200</v>
@@ -5103,24 +5005,24 @@
         <v>348</v>
       </c>
       <c r="H88" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B89" t="s">
-        <v>205</v>
+        <v>12</v>
       </c>
       <c r="C89" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D89" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="E89" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="F89" s="3">
         <v>100</v>
@@ -5129,24 +5031,24 @@
         <v>166</v>
       </c>
       <c r="H89" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B90" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C90" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D90" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="E90" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="F90" s="3">
         <v>10</v>
@@ -5155,24 +5057,24 @@
         <v>48</v>
       </c>
       <c r="H90" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>318</v>
+        <v>136</v>
       </c>
       <c r="C91" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="D91" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="E91" t="s">
-        <v>321</v>
+        <v>300</v>
       </c>
       <c r="F91" s="3">
         <v>5</v>
@@ -5181,24 +5083,24 @@
         <v>28.5</v>
       </c>
       <c r="H91" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>318</v>
+        <v>136</v>
       </c>
       <c r="C92" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="D92" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="E92" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="F92" s="3">
         <v>5</v>
@@ -5207,24 +5109,24 @@
         <v>28.5</v>
       </c>
       <c r="H92" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B93" t="s">
-        <v>205</v>
+        <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D93" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="E93" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="F93" s="3">
         <v>10</v>
@@ -5233,24 +5135,24 @@
         <v>25</v>
       </c>
       <c r="H93" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B94" t="s">
-        <v>205</v>
+        <v>12</v>
       </c>
       <c r="C94" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D94" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="E94" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="F94" s="3">
         <v>10</v>
@@ -5259,24 +5161,24 @@
         <v>68</v>
       </c>
       <c r="H94" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>256</v>
+        <v>84</v>
       </c>
       <c r="C95" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="D95" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="E95" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
       <c r="F95" s="3">
         <v>5</v>
@@ -5285,24 +5187,24 @@
         <v>68</v>
       </c>
       <c r="H95" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>256</v>
+        <v>84</v>
       </c>
       <c r="C96" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="D96" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="E96" t="s">
-        <v>329</v>
+        <v>308</v>
       </c>
       <c r="F96" s="3">
         <v>5</v>
@@ -5311,24 +5213,24 @@
         <v>68</v>
       </c>
       <c r="H96" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B97" t="s">
-        <v>330</v>
+        <v>245</v>
       </c>
       <c r="C97" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="D97" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="E97" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="F97" s="3">
         <v>10</v>
@@ -5337,24 +5239,24 @@
         <v>30</v>
       </c>
       <c r="H97" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B98" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="C98" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="D98" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="E98" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F98" s="3">
         <v>100</v>
@@ -5363,24 +5265,24 @@
         <v>175</v>
       </c>
       <c r="H98" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B99" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="C99" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="D99" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="E99" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="F99" s="3">
         <v>100</v>
@@ -5389,24 +5291,24 @@
         <v>175</v>
       </c>
       <c r="H99" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C100" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="D100" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="E100" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F100" s="3">
         <v>20</v>
@@ -5415,24 +5317,24 @@
         <v>35</v>
       </c>
       <c r="H100" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C101" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="D101" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="E101" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="F101" s="3">
         <v>20</v>
@@ -5441,24 +5343,24 @@
         <v>35</v>
       </c>
       <c r="H101" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B102" t="s">
-        <v>330</v>
+        <v>245</v>
       </c>
       <c r="C102" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="D102" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="F102" s="3">
         <v>4</v>
@@ -5467,24 +5369,24 @@
         <v>100</v>
       </c>
       <c r="H102" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B103" t="s">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="C103" t="s">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="D103" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="E103" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="F103" s="3">
         <v>10</v>
@@ -5493,24 +5395,24 @@
         <v>110</v>
       </c>
       <c r="H103" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B104" t="s">
-        <v>273</v>
+        <v>187</v>
       </c>
       <c r="C104" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="D104" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="E104" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="F104" s="3">
         <v>500</v>
@@ -5519,24 +5421,24 @@
         <v>196</v>
       </c>
       <c r="H104" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B105" t="s">
-        <v>348</v>
+        <v>8</v>
       </c>
       <c r="C105" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="D105" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="E105" t="s">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="F105" s="3">
         <v>1</v>
@@ -5545,24 +5447,24 @@
         <v>16</v>
       </c>
       <c r="H105" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B106" t="s">
-        <v>348</v>
+        <v>8</v>
       </c>
       <c r="C106" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="D106" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="E106" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F106" s="3">
         <v>1</v>
@@ -5571,24 +5473,24 @@
         <v>24</v>
       </c>
       <c r="H106" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B107" t="s">
-        <v>348</v>
+        <v>8</v>
       </c>
       <c r="C107" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="D107" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="E107" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F107" s="3">
         <v>1</v>
@@ -5597,24 +5499,24 @@
         <v>24</v>
       </c>
       <c r="H107" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B108" t="s">
-        <v>348</v>
+        <v>8</v>
       </c>
       <c r="C108" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="D108" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="E108" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F108" s="3">
         <v>1</v>
@@ -5623,24 +5525,24 @@
         <v>24</v>
       </c>
       <c r="H108" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B109" t="s">
-        <v>348</v>
+        <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="D109" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="E109" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F109" s="3">
         <v>1</v>
@@ -5649,24 +5551,24 @@
         <v>24</v>
       </c>
       <c r="H109" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B110" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C110" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D110" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="E110" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="F110" s="3">
         <v>100</v>
@@ -5675,24 +5577,24 @@
         <v>277.39999999999998</v>
       </c>
       <c r="H110" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B111" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="C111" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="D111" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="E111" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="F111" s="3">
         <v>100</v>
@@ -5701,24 +5603,24 @@
         <v>383</v>
       </c>
       <c r="H111" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="C112" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="D112" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="E112" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="F112" s="3">
         <v>50</v>
@@ -5727,24 +5629,24 @@
         <v>219</v>
       </c>
       <c r="H112" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B113" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="C113" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="D113" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="E113" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="F113" s="3">
         <v>100</v>
@@ -5753,24 +5655,24 @@
         <v>422</v>
       </c>
       <c r="H113" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B114" t="s">
-        <v>362</v>
+        <v>334</v>
       </c>
       <c r="C114" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D114" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="E114" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="F114" s="3">
         <v>100</v>
@@ -5779,24 +5681,24 @@
         <v>326</v>
       </c>
       <c r="H114" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B115" t="s">
-        <v>362</v>
+        <v>334</v>
       </c>
       <c r="C115" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D115" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="E115" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="F115" s="3">
         <v>100</v>
@@ -5805,24 +5707,24 @@
         <v>326</v>
       </c>
       <c r="H115" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B116" t="s">
-        <v>362</v>
+        <v>334</v>
       </c>
       <c r="C116" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D116" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="E116" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="F116" s="3">
         <v>100</v>
@@ -5831,24 +5733,24 @@
         <v>487</v>
       </c>
       <c r="H116" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B117" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C117" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D117" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="E117" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="F117" s="3">
         <v>100</v>
@@ -5857,24 +5759,24 @@
         <v>106.4</v>
       </c>
       <c r="H117" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B118" t="s">
-        <v>174</v>
+        <v>59</v>
       </c>
       <c r="C118" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="D118" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="E118" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="F118" s="3">
         <v>200</v>
@@ -5883,24 +5785,24 @@
         <v>190</v>
       </c>
       <c r="H118" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="C119" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="D119" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="E119" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="F119" s="3">
         <v>100</v>
@@ -5909,24 +5811,24 @@
         <v>57</v>
       </c>
       <c r="H119" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B120" t="s">
-        <v>375</v>
+        <v>230</v>
       </c>
       <c r="C120" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="D120" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="E120" t="s">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="F120" s="3">
         <v>200</v>
@@ -5935,24 +5837,24 @@
         <v>120</v>
       </c>
       <c r="H120" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B121" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="C121" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="D121" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="E121" t="s">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="F121" s="3">
         <v>50</v>
@@ -5961,24 +5863,24 @@
         <v>58</v>
       </c>
       <c r="H121" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B122" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C122" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="D122" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="E122" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="F122" s="3">
         <v>100</v>
@@ -5987,24 +5889,24 @@
         <v>74</v>
       </c>
       <c r="H122" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B123" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="C123" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="D123" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="E123" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="F123" s="3">
         <v>100</v>
@@ -6013,24 +5915,24 @@
         <v>49</v>
       </c>
       <c r="H123" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B124" t="s">
-        <v>191</v>
+        <v>124</v>
       </c>
       <c r="C124" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="D124" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="E124" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="F124" s="3">
         <v>100</v>
@@ -6039,24 +5941,24 @@
         <v>104</v>
       </c>
       <c r="H124" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C125" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="D125" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="E125" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F125" s="3">
         <v>1</v>
@@ -6065,24 +5967,24 @@
         <v>198</v>
       </c>
       <c r="H125" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B126" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C126" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D126" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="E126" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="F126" s="3">
         <v>1</v>
@@ -6091,24 +5993,24 @@
         <v>19</v>
       </c>
       <c r="H126" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B127" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="C127" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D127" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="E127" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="F127" s="3">
         <v>200</v>
@@ -6117,24 +6019,24 @@
         <v>772</v>
       </c>
       <c r="H127" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B128" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="C128" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D128" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="E128" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="F128" s="3">
         <v>40</v>
@@ -6143,24 +6045,24 @@
         <v>177</v>
       </c>
       <c r="H128" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B129" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="C129" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D129" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="E129" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="F129" s="3">
         <v>40</v>
@@ -6169,24 +6071,24 @@
         <v>197</v>
       </c>
       <c r="H129" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>205</v>
+        <v>12</v>
       </c>
       <c r="C130" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D130" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="E130" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="F130" s="3">
         <v>20</v>
@@ -6195,24 +6097,24 @@
         <v>58</v>
       </c>
       <c r="H130" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B131" t="s">
-        <v>205</v>
+        <v>12</v>
       </c>
       <c r="C131" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D131" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="E131" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="F131" s="3">
         <v>20</v>
@@ -6221,24 +6123,24 @@
         <v>58</v>
       </c>
       <c r="H131" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B132" t="s">
-        <v>205</v>
+        <v>12</v>
       </c>
       <c r="C132" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D132" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="E132" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="F132" s="3">
         <v>20</v>
@@ -6247,24 +6149,24 @@
         <v>68</v>
       </c>
       <c r="H132" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B133" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C133" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="D133" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="E133" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="F133" s="3">
         <v>20</v>
@@ -6273,24 +6175,24 @@
         <v>123</v>
       </c>
       <c r="H133" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>395</v>
+        <v>136</v>
       </c>
       <c r="C134" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="E134" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F134" s="3">
         <v>100</v>
@@ -6299,24 +6201,24 @@
         <v>840</v>
       </c>
       <c r="H134" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B135" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="C135" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="D135" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="E135" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="F135" s="3">
         <v>10</v>
@@ -6325,24 +6227,24 @@
         <v>73</v>
       </c>
       <c r="H135" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>402</v>
+        <v>34</v>
       </c>
       <c r="C136" t="s">
-        <v>403</v>
+        <v>376</v>
       </c>
       <c r="D136" t="s">
-        <v>404</v>
+        <v>377</v>
       </c>
       <c r="E136" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F136" s="3">
         <v>50</v>
@@ -6351,24 +6253,24 @@
         <v>223</v>
       </c>
       <c r="H136" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C137" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="D137" t="s">
-        <v>405</v>
+        <v>378</v>
       </c>
       <c r="E137" t="s">
-        <v>406</v>
+        <v>379</v>
       </c>
       <c r="F137" s="3">
         <v>20</v>
@@ -6377,24 +6279,24 @@
         <v>103</v>
       </c>
       <c r="H137" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B138" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C138" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D138" t="s">
-        <v>407</v>
+        <v>380</v>
       </c>
       <c r="E138" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="F138" s="3">
         <v>1</v>
@@ -6403,24 +6305,24 @@
         <v>28</v>
       </c>
       <c r="H138" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>408</v>
+        <v>84</v>
       </c>
       <c r="C139" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="D139" t="s">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="E139" t="s">
-        <v>411</v>
+        <v>383</v>
       </c>
       <c r="F139" s="3">
         <v>10</v>
@@ -6429,24 +6331,24 @@
         <v>207</v>
       </c>
       <c r="H139" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B140" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C140" t="s">
-        <v>412</v>
+        <v>384</v>
       </c>
       <c r="D140" t="s">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="E140" t="s">
-        <v>413</v>
+        <v>385</v>
       </c>
       <c r="F140" s="3">
         <v>5</v>
@@ -6455,24 +6357,24 @@
         <v>150</v>
       </c>
       <c r="H140" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B141" t="s">
-        <v>414</v>
+        <v>55</v>
       </c>
       <c r="C141" t="s">
-        <v>415</v>
+        <v>386</v>
       </c>
       <c r="D141" t="s">
-        <v>416</v>
+        <v>387</v>
       </c>
       <c r="E141" t="s">
-        <v>417</v>
+        <v>388</v>
       </c>
       <c r="F141" s="3">
         <v>1</v>
@@ -6481,24 +6383,24 @@
         <v>79</v>
       </c>
       <c r="H141" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B142" t="s">
-        <v>418</v>
+        <v>55</v>
       </c>
       <c r="C142" t="s">
-        <v>415</v>
+        <v>386</v>
       </c>
       <c r="D142" t="s">
-        <v>416</v>
+        <v>387</v>
       </c>
       <c r="E142" t="s">
-        <v>419</v>
+        <v>389</v>
       </c>
       <c r="F142" s="3">
         <v>5</v>
@@ -6507,24 +6409,24 @@
         <v>140</v>
       </c>
       <c r="H142" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B143" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C143" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D143" t="s">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="E143" t="s">
-        <v>421</v>
+        <v>391</v>
       </c>
       <c r="F143" s="3">
         <v>100</v>
@@ -6533,24 +6435,24 @@
         <v>257.39999999999998</v>
       </c>
       <c r="H143" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B144" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C144" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D144" t="s">
-        <v>422</v>
+        <v>392</v>
       </c>
       <c r="E144" t="s">
-        <v>423</v>
+        <v>393</v>
       </c>
       <c r="F144" s="3">
         <v>100</v>
@@ -6559,24 +6461,24 @@
         <v>190.4</v>
       </c>
       <c r="H144" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B145" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
       <c r="C145" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D145" t="s">
-        <v>425</v>
+        <v>395</v>
       </c>
       <c r="E145" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="F145" s="3">
         <v>100</v>
@@ -6585,24 +6487,24 @@
         <v>150</v>
       </c>
       <c r="H145" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C146" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D146" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="E146" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="F146" s="3">
         <v>100</v>
@@ -6611,24 +6513,24 @@
         <v>72</v>
       </c>
       <c r="H146" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C147" t="s">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="D147" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="E147" t="s">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="F147" s="3">
         <v>1</v>
@@ -6637,24 +6539,24 @@
         <v>137</v>
       </c>
       <c r="H147" t="s">
-        <v>431</v>
+        <v>140</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B148" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C148" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="D148" t="s">
-        <v>432</v>
+        <v>401</v>
       </c>
       <c r="E148" t="s">
-        <v>433</v>
+        <v>402</v>
       </c>
       <c r="F148" s="3">
         <v>50</v>
@@ -6663,24 +6565,24 @@
         <v>99</v>
       </c>
       <c r="H148" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B149" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C149" t="s">
-        <v>434</v>
+        <v>403</v>
       </c>
       <c r="D149" t="s">
-        <v>435</v>
+        <v>404</v>
       </c>
       <c r="E149" t="s">
-        <v>436</v>
+        <v>405</v>
       </c>
       <c r="F149" s="3">
         <v>10</v>
@@ -6689,11 +6591,11 @@
         <v>105</v>
       </c>
       <c r="H149" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>